--- a/activities/05 - Hold the Gain and Hand Over/data/A05-Data-Workbook.xlsx
+++ b/activities/05 - Hold the Gain and Hand Over/data/A05-Data-Workbook.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Certified Lean Six Sigma White Belt (CLSSWB) Training  ·  TGS-2025053210  ·  Version v4</t>
+          <t>Certified Lean Six Sigma White Belt (CLSSWB) Training  ·  TGS-2025053210  ·  Version v5</t>
         </is>
       </c>
     </row>

--- a/activities/05 - Hold the Gain and Hand Over/data/A05-Data-Workbook.xlsx
+++ b/activities/05 - Hold the Gain and Hand Over/data/A05-Data-Workbook.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Certified Lean Six Sigma White Belt (CLSSWB) Training  ·  TGS-2025053210  ·  Version v5</t>
+          <t>Certified Lean Six Sigma White Belt (CLSSWB) Training  ·  TGS-2025053210  ·  Version v6</t>
         </is>
       </c>
     </row>

--- a/activities/05 - Hold the Gain and Hand Over/data/A05-Data-Workbook.xlsx
+++ b/activities/05 - Hold the Gain and Hand Over/data/A05-Data-Workbook.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Certified Lean Six Sigma White Belt (CLSSWB) Training  ·  TGS-2025053210  ·  Version v6</t>
+          <t>Certified Lean Six Sigma White Belt (CLSSWB) Training  ·  TGS-2025053210  ·  Version v7</t>
         </is>
       </c>
     </row>
